--- a/survey_templates/027_relationship_questionnaire--survey_templates.xlsx
+++ b/survey_templates/027_relationship_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>how_do_you_feel</t>
+          <t>relationship_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How do you feel</t>
+          <t>Relationship Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>relationship_status</t>
+          <t>relationship_length</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is your relationship status</t>
+          <t>Relationship Length</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>relationship_length</t>
+          <t>relationship_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How long have you been in a relationship</t>
+          <t>Relationship Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>relationship_type</t>
+          <t>relationship_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What type of relationship do you have</t>
+          <t>How Satisfied Are You with Your Relationship?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>relationship_satisfaction</t>
+          <t>relationship_conflicts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How satisfied are you with your relationship</t>
+          <t>Do You Often Have Conflicts?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>relationship_conflicts</t>
+          <t>relationship_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Do you often have conflicts</t>
+          <t>Do You Feel Supported?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>relationship_support</t>
+          <t>relationship_quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Do you feel supported</t>
+          <t>Relationship Quality</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>relationship_quality</t>
+          <t>relationship_dominance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How would you rate the quality of your relationship</t>
+          <t>Do You Feel Dominant?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>relationship_dominance</t>
+          <t>relationship_satisfaction_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Do you feel dominant in your relationship</t>
+          <t>How Satisfied Are You with Your Relationship (Scale 1-10)?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>relationship_satisfaction_2</t>
+          <t>relationship_conflicts_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How satisfied are you with your relationship</t>
+          <t>How Often Do You Have Conflicts (Scale 1-10)?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>relationship_conflicts_2</t>
+          <t>relationship_support_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often do you have conflicts</t>
+          <t>How Much Do You Feel Supported (Scale 1-10)?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>relationship_support_2</t>
+          <t>relationship_quality_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How much do you feel supported</t>
+          <t>How Would You Rate the Quality of Your Relationship (Scale 1-10)?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>relationship_quality_2</t>
+          <t>relationship_dominance_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How would you rate the quality of your relationship</t>
+          <t>How Much Do You Feel Dominant (Scale 1-10)?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>relationship_dominance_2</t>
+          <t>relationship_satisfaction_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How much do you feel dominant</t>
+          <t>Relationship Satisfaction 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>relationship_satisfaction_3</t>
+          <t>relationship_conflicts_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How satisfied are you with your relationship</t>
+          <t>How Often Do You Have Conflicts?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>relationship_conflicts_3</t>
+          <t>relationship_support_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How often do you have conflicts</t>
+          <t>How Much Do You Feel Supported?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>relationship_support_3</t>
+          <t>relationship_quality_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How much do you feel supported</t>
+          <t>How Would You Rate the Quality of Your Relationship?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>relationship_quality_3</t>
+          <t>relationship_dominance_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How would you rate the quality of your relationship</t>
+          <t>How Much Do You Feel Dominant?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>relationship_dominance_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How much do you feel dominant</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>relationship_satisfaction_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How satisfied are you with your relationship</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>relationship_conflicts_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How often do you have conflicts</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>relationship_support_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How much do you feel supported</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>relationship_satisfaction_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How satisfied are you with your relationship</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>relationship_conflicts_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How often do you have conflicts</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>relationship_support_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How much do you feel supported</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1126,68 +965,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>how_do_you_feel_choices</t>
+          <t>relationship_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>how_do_you_feel_choices</t>
+          <t>relationship_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>how_do_you_feel_choices</t>
+          <t>relationship_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>how_do_you_feel_choices</t>
+          <t>relationship_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>excited</t>
+          <t>engaged</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Excited</t>
+          <t>Engaged</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>in_a_relationship</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>In a relationship</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
@@ -1233,80 +1072,80 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>it's_complicated</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>It's complicated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>relationship_status_choices</t>
+          <t>relationship_length_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>engaged</t>
+          <t>less_than_1_month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Engaged</t>
+          <t>Less than 1 month</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>relationship_status_choices</t>
+          <t>relationship_length_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>widowed</t>
+          <t>1-3_months</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Widowed</t>
+          <t>1-3 months</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>relationship_status_choices</t>
+          <t>relationship_length_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>separated</t>
+          <t>3-6_months</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Separated</t>
+          <t>3-6 months</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>relationship_status_choices</t>
+          <t>relationship_length_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>it's_complicated</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>It's complicated</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>less_than_1_month</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Less than 1 month</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1-3_months</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1-3 months</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3-6_months</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3-6 months</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
@@ -1369,80 +1208,80 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6-12_months</t>
+          <t>never_been_in_a_relationship</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6-12 months</t>
+          <t>Never been in a relationship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>relationship_length_choices</t>
+          <t>relationship_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1-2_years</t>
+          <t>casual</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1-2 years</t>
+          <t>Casual</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>relationship_length_choices</t>
+          <t>relationship_type_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2-5_years</t>
+          <t>romantic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2-5 years</t>
+          <t>Romantic</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>relationship_length_choices</t>
+          <t>relationship_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>more_than_5_years</t>
+          <t>friendly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>More than 5 years</t>
+          <t>Friendly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>relationship_length_choices</t>
+          <t>relationship_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>never_been_in_a_relationship</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Never been in a relationship</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1454,503 +1293,401 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>casual</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Casual</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>relationship_type_choices</t>
+          <t>relationship_satisfaction_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>romantic</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romantic</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>relationship_type_choices</t>
+          <t>relationship_satisfaction_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>friendly</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Friendly</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>relationship_type_choices</t>
+          <t>relationship_satisfaction_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Neither satisfied nor dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>relationship_type_choices</t>
+          <t>relationship_satisfaction_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>relationship_type_choices</t>
+          <t>relationship_satisfaction_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>don't_know</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>relationship_type_choices</t>
+          <t>relationship_conflicts_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>relationship_satisfaction_choices</t>
+          <t>relationship_conflicts_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>relationship_satisfaction_choices</t>
+          <t>relationship_conflicts_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Somewhat satisfied</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>relationship_satisfaction_choices</t>
+          <t>relationship_conflicts_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>neither_satisfied_nor_dissatisfied</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Neither satisfied nor dissatisfied</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>relationship_satisfaction_choices</t>
+          <t>relationship_support_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Somewhat dissatisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>relationship_satisfaction_choices</t>
+          <t>relationship_support_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Very dissatisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>relationship_conflicts_choices</t>
+          <t>relationship_support_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>relationship_conflicts_choices</t>
+          <t>relationship_support_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>relationship_conflicts_choices</t>
+          <t>relationship_support_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>don't_know</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Don't know</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>relationship_conflicts_choices</t>
+          <t>relationship_quality_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>relationship_support_choices</t>
+          <t>relationship_quality_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>relationship_support_choices</t>
+          <t>relationship_quality_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>relationship_support_choices</t>
+          <t>relationship_quality_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>minimal</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>Minimal</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>relationship_support_choices</t>
+          <t>relationship_dominance_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>don't_know</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>relationship_support_choices</t>
+          <t>relationship_dominance_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>not_sure</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Not sure</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>relationship_quality_choices</t>
+          <t>relationship_dominance_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>relationship_quality_choices</t>
+          <t>relationship_dominance_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>relationship_quality_choices</t>
+          <t>relationship_dominance_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>don't_know</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>relationship_quality_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>minimalist</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Minimalist</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>relationship_dominance_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>relationship_dominance_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>relationship_dominance_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>relationship_dominance_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>not_sure</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>relationship_dominance_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>don't_know</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
         <is>
           <t>Don't know</t>
         </is>
